--- a/Data/GB.xlsx
+++ b/Data/GB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yair\Documents\yair\research\estuary_rehabilitation\yairs_stuff\Students\Noam\TaxoTox\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5DD2BE4-663A-4446-B560-E475EC1D38C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{103367CA-C978-469B-A926-4D83433EF2E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -67,9 +67,6 @@
     <t>Acetaminophen</t>
   </si>
   <si>
-    <t>Sulfadiazine</t>
-  </si>
-  <si>
     <t>Sulfapyridine</t>
   </si>
   <si>
@@ -139,7 +136,10 @@
     <t>Compound</t>
   </si>
   <si>
-    <t>Lincomycinn</t>
+    <t>Lincomycin</t>
+  </si>
+  <si>
+    <t>Sulfadiazinee</t>
   </si>
 </sst>
 </file>
@@ -478,7 +478,7 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -572,7 +572,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3">
         <v>192.22800000000001</v>
@@ -619,7 +619,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B4">
         <v>14.506</v>
@@ -666,7 +666,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5">
         <v>127.604</v>
@@ -713,7 +713,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6">
         <v>107.39</v>
@@ -760,7 +760,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7">
         <v>415.75400000000002</v>
@@ -807,7 +807,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>1978.058</v>
@@ -854,7 +854,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>412.78300000000002</v>
@@ -901,7 +901,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>299.18599999999998</v>
@@ -948,7 +948,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B11">
         <v>15.111000000000001</v>
@@ -995,7 +995,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B12">
         <v>13.419</v>
@@ -1042,7 +1042,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B13">
         <v>196.96</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B14">
         <v>1508.4880000000001</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B15">
         <v>82.158000000000001</v>
@@ -1183,7 +1183,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B16">
         <v>154.61500000000001</v>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>25.614000000000001</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B18">
         <v>154.85300000000001</v>
@@ -1324,7 +1324,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -1371,7 +1371,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -1418,7 +1418,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B21">
         <v>10</v>
@@ -1465,7 +1465,7 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B22">
         <v>1261.856</v>
@@ -1512,7 +1512,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23">
         <v>12.786</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24">
         <v>1555.357</v>
@@ -1606,7 +1606,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B25">
         <v>162.66499999999999</v>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B26">
         <v>177.88300000000001</v>
